--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260908.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260908.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,7 +611,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>6,118,000</t>
+          <t>6,279,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -633,34 +633,34 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>10,467,000</t>
+          <t>10,621,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>3.81%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>6,282,000</t>
+          <t>4,947,261,681</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>21,729,000</t>
+          <t>22,163,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -699,100 +699,100 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>48,962,000</t>
+          <t>49,710,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>10,202,000</t>
+          <t>6,282,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>35,782,000</t>
+          <t>10,202,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>20,733,000</t>
+          <t>35,782,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,004,464,049</t>
+          <t>21,691,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>11,465,000</t>
+          <t>11,759,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>3,948,000</t>
+          <t>4,004,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
@@ -880,95 +880,95 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>6,769,000</t>
+          <t>26,264,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>26,264,000</t>
+          <t>6,846,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>22,876,000</t>
+          <t>34,858,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>34,858,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>37,920,000</t>
+          <t>38,455,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>9,637,000</t>
+          <t>9,766,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>9,594,000</t>
+          <t>4,364,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,66 +1063,66 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>4,364,000</t>
+          <t>2,270,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,225,000</t>
+          <t>2,939,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,893,000</t>
+          <t>9,594,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>18,088,000</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,295,000</t>
+          <t>18,088,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,346,000</t>
+          <t>15,295,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,763,521,747</t>
+          <t>2,716,169,590</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>41,257,000</t>
+          <t>42,169,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>16,725,000</t>
+          <t>17,277,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>7,920,000</t>
+          <t>7,991,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -1408,51 +1408,51 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>10,287,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>10,287,000</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1584,68 +1584,68 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>202610WTX</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>115/10台股期貨</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>48,390,000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>1,593,000</t>
+          <t>52,799,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>18,948,000</t>
+          <t>48,390,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,132 +1657,154 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>52,799,000</t>
+          <t>1,593,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>6,733,000</t>
+          <t>18,948,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>16,823,000</t>
+          <t>6,733,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>18,491,000</t>
+          <t>16,823,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>長華電材</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>18,224,000</t>
+          <t>18,491,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>長華電材</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>18,224,000</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
           <t>PB_NTD</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>PAYABLES</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>-1,471,682</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>-232,568,792</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
         </is>
       </c>
     </row>
